--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75185515</v>
+        <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92632</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442438</v>
+        <v>442493</v>
       </c>
       <c r="R2" t="n">
-        <v>7047753</v>
+        <v>7047884</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofie Jonsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75185515</t>
+          <t>https://artportalen.se/Sighting/136654515</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135121278</v>
+        <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>58006</v>
+        <v>92098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,38 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Koltjärnen, Jmt</t>
+          <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442483</v>
+        <v>442183</v>
       </c>
       <c r="R3" t="n">
-        <v>7047683</v>
+        <v>7047999</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,27 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,16 +898,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121278</t>
+          <t>https://artportalen.se/Sighting/136654535</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135121292</v>
+        <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>58006</v>
+        <v>92098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Koltjärnen, Jmt</t>
+          <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442275</v>
+        <v>442117</v>
       </c>
       <c r="R4" t="n">
-        <v>7047784</v>
+        <v>7047912</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,27 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,16 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1033,16 +1010,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121292</t>
+          <t>https://artportalen.se/Sighting/136654547</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135121293</v>
+        <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>58006</v>
+        <v>92098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Koltjärnen, Jmt</t>
+          <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442387</v>
+        <v>442105</v>
       </c>
       <c r="R5" t="n">
-        <v>7047735</v>
+        <v>7047919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,27 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,16 +1107,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1165,16 +1122,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121293</t>
+          <t>https://artportalen.se/Sighting/136654548</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135121294</v>
+        <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>58006</v>
+        <v>92098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Koltjärnen, Jmt</t>
+          <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442493</v>
+        <v>442108</v>
       </c>
       <c r="R6" t="n">
-        <v>7047717</v>
+        <v>7047845</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,27 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,16 +1219,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1297,7 +1234,4120 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136654553</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136654573</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92098</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>442177</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7047948</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654573</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136654582</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92098</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>441954</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7047896</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654582</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136654519</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92102</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>442424</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7047868</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654519</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136654600</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92534</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>442389</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7047649</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654600</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>75185515</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>442438</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7047753</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sofie Jonsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75185515</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136654541</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>442105</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7048020</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654541</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136654563</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>442036</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7047788</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654563</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136654564</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>442100</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7047801</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654564</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135121278</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>442483</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7047683</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121278</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135121292</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>442275</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7047784</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121292</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135121293</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>442387</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7047735</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121293</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135121294</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Koltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>442493</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7047717</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135121294</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136654514</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>442522</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7047840</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654514</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136654517</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>442468</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7047891</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654517</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136654520</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>442400</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7047849</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654520</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136654522</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>442356</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7047826</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bohål ca 1,5m upp i tajgagrantickerötad gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654522</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136654524</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>442364</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7047807</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654524</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136654525</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>442340</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7047822</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654525</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136654528</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>442327</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7047837</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654528</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136654530</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>442319</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7047832</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654530</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136654534</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>442200</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7048000</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654534</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136654545</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>442135</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7047932</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654545</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136654555</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>442023</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7047925</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654555</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136654557</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>441918</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7047898</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654557</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136654559</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>441935</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7047862</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654559</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136654567</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>442181</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7047878</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654567</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136654568</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>442182</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7047892</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654568</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136654590</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>442203</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7047845</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654590</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136654593</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>442213</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7047860</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654593</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136654601</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>442408</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7047655</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654601</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136654603</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>442429</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7047660</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654603</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136654613</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>442619</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7047612</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654613</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136654526</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>442341</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7047839</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654526</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136654587</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58110</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>441985</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7047804</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136654587</t>
         </is>
       </c>
     </row>
@@ -1308,6 +5358,40 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136654541</v>
       </c>
       <c r="B12" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136654563</v>
       </c>
       <c r="B13" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136654564</v>
       </c>
       <c r="B14" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136654514</v>
       </c>
       <c r="B19" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136654517</v>
       </c>
       <c r="B20" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136654520</v>
       </c>
       <c r="B21" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>136654522</v>
       </c>
       <c r="B22" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136654524</v>
       </c>
       <c r="B23" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136654525</v>
       </c>
       <c r="B24" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136654528</v>
       </c>
       <c r="B25" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136654530</v>
       </c>
       <c r="B26" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>136654534</v>
       </c>
       <c r="B27" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>136654545</v>
       </c>
       <c r="B28" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136654555</v>
       </c>
       <c r="B29" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>136654557</v>
       </c>
       <c r="B30" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>136654559</v>
       </c>
       <c r="B31" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136654567</v>
       </c>
       <c r="B32" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>136654568</v>
       </c>
       <c r="B33" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>136654590</v>
       </c>
       <c r="B34" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>136654593</v>
       </c>
       <c r="B35" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136654601</v>
       </c>
       <c r="B36" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>136654603</v>
       </c>
       <c r="B37" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>136654613</v>
       </c>
       <c r="B38" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>136654526</v>
       </c>
       <c r="B39" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>136654587</v>
       </c>
       <c r="B40" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136654541</v>
       </c>
       <c r="B12" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136654563</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136654564</v>
       </c>
       <c r="B14" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136654514</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136654517</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136654520</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>136654522</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136654524</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136654525</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136654528</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136654530</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>136654534</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>136654545</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136654555</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>136654557</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>136654559</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136654567</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>136654568</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>136654590</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>136654593</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136654601</v>
       </c>
       <c r="B36" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>136654603</v>
       </c>
       <c r="B37" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>136654613</v>
       </c>
       <c r="B38" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>136654526</v>
       </c>
       <c r="B39" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>136654587</v>
       </c>
       <c r="B40" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 33021-2026 artfynd.xlsx
+++ b/artfynd/A 33021-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136654515</v>
       </c>
       <c r="B2" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136654535</v>
       </c>
       <c r="B3" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136654547</v>
       </c>
       <c r="B4" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136654548</v>
       </c>
       <c r="B5" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136654553</v>
       </c>
       <c r="B6" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136654573</v>
       </c>
       <c r="B7" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136654582</v>
       </c>
       <c r="B8" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136654519</v>
       </c>
       <c r="B9" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136654600</v>
       </c>
       <c r="B10" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136654541</v>
       </c>
       <c r="B12" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136654563</v>
       </c>
       <c r="B13" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136654564</v>
       </c>
       <c r="B14" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136654514</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136654517</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136654520</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>136654522</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136654524</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136654525</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136654528</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136654530</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>136654534</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>136654545</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>136654555</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>136654557</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>136654559</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136654567</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>136654568</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>136654590</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>136654593</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136654601</v>
       </c>
       <c r="B36" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>136654603</v>
       </c>
       <c r="B37" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>136654613</v>
       </c>
       <c r="B38" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>136654526</v>
       </c>
       <c r="B39" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>136654587</v>
       </c>
       <c r="B40" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
